--- a/reports/pdf_weekly_20260710.xlsx
+++ b/reports/pdf_weekly_20260710.xlsx
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K57"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,14 +567,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>주간 변화  ·  2026-07-06 ~ 2026-07-10  (5거래일)  ·  캡처 6/7  ·  대기: TIGER</t>
+          <t>주간 변화  ·  2026-07-06 ~ 2026-07-10  (5거래일)  ·  캡처 5/7  ·  대기: PLUS, TIGER</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,389억      주말 2026-07-10  vs  주초 2026-07-06      매수 14종목  /  매도 14종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,448억      주말 2026-07-10  vs  주초 2026-07-06      매수 14종목  /  매도 14종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>109</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>939340200</v>
+        <v>877815150</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-54</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-875698560</v>
+        <v>-818341920</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>93</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1038363600</v>
+        <v>970352700</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-52</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-1567030400</v>
+        <v>-1464392800</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>66</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>2443227600</v>
+        <v>2283200700</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-37</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-1251369600</v>
+        <v>-1169407200</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>60</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>4669872000</v>
+        <v>4364004000</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>-25</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-3929500000</v>
+        <v>-3672125000</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>21</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>1971362400</v>
+        <v>1842241800</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>-23</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-2615366800</v>
+        <v>-2444065100</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>20</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>1205408000</v>
+        <v>1126456000</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>-22</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-492461200</v>
+        <v>-460205900</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>16</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1347628800</v>
+        <v>1259361600</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>-20</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-904056000</v>
+        <v>-844842000</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>11</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>556850800</v>
+        <v>520378100</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>-19</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-1377872400</v>
+        <v>-1287624300</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>11</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>460266400</v>
+        <v>430119800</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>-17</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-902972000</v>
+        <v>-843829000</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -1059,23 +1059,23 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>와이지엔터테인먼트</t>
+          <t>동진쎄미켐</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>444982000</v>
+        <v>436603000</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>0.23%→0.35%</t>
+          <t>1.82%→1.86%</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>27→37</t>
+          <t>178→188</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -1087,7 +1087,7 @@
         <v>-16</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-2639756800</v>
+        <v>-2466857600</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1103,23 +1103,23 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>동진쎄미켐</t>
+          <t>와이지엔터테인먼트</t>
         </is>
       </c>
       <c r="B16" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>467204000</v>
+        <v>415836500</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>1.82%→1.86%</t>
+          <t>0.23%→0.35%</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>178→188</t>
+          <t>27→37</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -1131,7 +1131,7 @@
         <v>-12</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-457881600</v>
+        <v>-427891200</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>8</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>1022428800</v>
+        <v>955461600</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>-10</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-462868000</v>
+        <v>-432551000</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>5</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>1626000000</v>
+        <v>1519500000</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>-6</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-985356000</v>
+        <v>-920817000</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>5</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>1674780000</v>
+        <v>1565085000</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>-4</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-512515200</v>
+        <v>-478946400</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
     <row r="21" ht="19" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,354억      주말 2026-07-10  vs  주초 2026-07-06      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,303억      주말 2026-07-10  vs  주초 2026-07-06      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B21" s="4" t="n"/>
@@ -1303,7 +1303,7 @@
     <row r="24" ht="19" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,513억      주말 2026-07-10  vs  주초 2026-07-06      매수 4종목  /  매도 5종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,562억      주말 2026-07-10  vs  주초 2026-07-06      매수 4종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B24" s="4" t="n"/>
@@ -1399,7 +1399,7 @@
         <v>201</v>
       </c>
       <c r="C27" s="11" t="n">
-        <v>6222397200</v>
+        <v>5330158200</v>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>-86</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-7235162800</v>
+        <v>-6197701800</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>139</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>7781164400</v>
+        <v>6665411400</v>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>-81</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-5047547400</v>
+        <v>-4323771900</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>35</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>8673630000</v>
+        <v>7429905000</v>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>-66</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-7675140000</v>
+        <v>-6574590000</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>17</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>1611538800</v>
+        <v>1380457800</v>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>-58</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-1637363200</v>
+        <v>-1402579200</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>-40</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>-4860120000</v>
+        <v>-4163220000</v>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
     <row r="33" ht="19" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,581억      주말 2026-07-10  vs  주초 2026-07-06      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,548억      주말 2026-07-10  vs  주초 2026-07-06      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B33" s="4" t="n"/>
@@ -1618,768 +1618,78 @@
       </c>
     </row>
     <row r="36" ht="19" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 324억      주말 2026-07-10  vs  주초 2026-07-06      매수 14종목  /  매도 14종목</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="n"/>
-      <c r="C36" s="4" t="n"/>
-      <c r="D36" s="4" t="n"/>
-      <c r="E36" s="4" t="n"/>
-      <c r="F36" s="4" t="n"/>
-      <c r="G36" s="4" t="n"/>
-      <c r="H36" s="4" t="n"/>
-      <c r="I36" s="4" t="n"/>
-      <c r="J36" s="4" t="n"/>
-      <c r="K36" s="4" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="n"/>
-      <c r="C37" s="6" t="n"/>
-      <c r="D37" s="6" t="n"/>
-      <c r="E37" s="6" t="n"/>
-      <c r="G37" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H37" s="8" t="n"/>
-      <c r="I37" s="8" t="n"/>
-      <c r="J37" s="8" t="n"/>
-      <c r="K37" s="8" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B38" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C38" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D38" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E38" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G38" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H38" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I38" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J38" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K38" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+        </is>
+      </c>
+      <c r="B36" s="20" t="n"/>
+      <c r="C36" s="20" t="n"/>
+      <c r="D36" s="20" t="n"/>
+      <c r="E36" s="20" t="n"/>
+      <c r="F36" s="20" t="n"/>
+      <c r="G36" s="20" t="n"/>
+      <c r="H36" s="20" t="n"/>
+      <c r="I36" s="20" t="n"/>
+      <c r="J36" s="20" t="n"/>
+      <c r="K36" s="20" t="n"/>
+    </row>
+    <row r="38" ht="19" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 568억      주말 2026-07-10  vs  주초 2026-07-06      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="n"/>
+      <c r="C38" s="4" t="n"/>
+      <c r="D38" s="4" t="n"/>
+      <c r="E38" s="4" t="n"/>
+      <c r="F38" s="4" t="n"/>
+      <c r="G38" s="4" t="n"/>
+      <c r="H38" s="4" t="n"/>
+      <c r="I38" s="4" t="n"/>
+      <c r="J38" s="4" t="n"/>
+      <c r="K38" s="4" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="inlineStr">
-        <is>
-          <t>더블유씨피</t>
-        </is>
-      </c>
-      <c r="B39" s="11" t="n">
-        <v>121</v>
-      </c>
-      <c r="C39" s="11" t="n">
-        <v>84361200</v>
-      </c>
-      <c r="D39" s="12" t="inlineStr">
-        <is>
-          <t>6.62%→6.85%</t>
-        </is>
-      </c>
-      <c r="E39" s="13" t="inlineStr">
-        <is>
-          <t>3,020→3,141</t>
-        </is>
-      </c>
-      <c r="G39" s="14" t="inlineStr">
-        <is>
-          <t>씨에스베어링</t>
-        </is>
-      </c>
-      <c r="H39" s="15" t="n">
-        <v>-318</v>
-      </c>
-      <c r="I39" s="15" t="n">
-        <v>-100837800</v>
-      </c>
-      <c r="J39" s="16" t="inlineStr">
-        <is>
-          <t>3.05%→2.71%</t>
-        </is>
-      </c>
-      <c r="K39" s="13" t="inlineStr">
-        <is>
-          <t>3,054→2,736</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="10" t="inlineStr">
-        <is>
-          <t>에이프로</t>
-        </is>
-      </c>
-      <c r="B40" s="11" t="n">
-        <v>91</v>
-      </c>
-      <c r="C40" s="11" t="n">
-        <v>21479640</v>
-      </c>
-      <c r="D40" s="12" t="inlineStr">
-        <is>
-          <t>0.38%→0.44%</t>
-        </is>
-      </c>
-      <c r="E40" s="13" t="inlineStr">
-        <is>
-          <t>510→601</t>
-        </is>
-      </c>
-      <c r="G40" s="14" t="inlineStr">
-        <is>
-          <t>LS증권</t>
-        </is>
-      </c>
-      <c r="H40" s="15" t="n">
-        <v>-101</v>
-      </c>
-      <c r="I40" s="15" t="n">
-        <v>-54552120</v>
-      </c>
-      <c r="J40" s="16" t="inlineStr">
-        <is>
-          <t>0.48%→0.31%</t>
-        </is>
-      </c>
-      <c r="K40" s="13" t="inlineStr">
-        <is>
-          <t>285→184</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="10" t="inlineStr">
-        <is>
-          <t>인텍플러스</t>
-        </is>
-      </c>
-      <c r="B41" s="11" t="n">
-        <v>54</v>
-      </c>
-      <c r="C41" s="11" t="n">
-        <v>181440000</v>
-      </c>
-      <c r="D41" s="12" t="inlineStr">
-        <is>
-          <t>1.97%→2.52%</t>
-        </is>
-      </c>
-      <c r="E41" s="13" t="inlineStr">
-        <is>
-          <t>186→240</t>
-        </is>
-      </c>
-      <c r="G41" s="14" t="inlineStr">
-        <is>
-          <t>씨어스</t>
-        </is>
-      </c>
-      <c r="H41" s="15" t="n">
-        <v>-36</v>
-      </c>
-      <c r="I41" s="15" t="n">
-        <v>-102211200</v>
-      </c>
-      <c r="J41" s="16" t="inlineStr">
-        <is>
-          <t>6.55%→6.19%</t>
-        </is>
-      </c>
-      <c r="K41" s="13" t="inlineStr">
-        <is>
-          <t>733→697</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="10" t="inlineStr">
-        <is>
-          <t>네패스아크</t>
-        </is>
-      </c>
-      <c r="B42" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="C42" s="11" t="n">
-        <v>41798400</v>
-      </c>
-      <c r="D42" s="12" t="inlineStr">
-        <is>
-          <t>0.17%→0.30%</t>
-        </is>
-      </c>
-      <c r="E42" s="13" t="inlineStr">
-        <is>
-          <t>21→37</t>
-        </is>
-      </c>
-      <c r="G42" s="14" t="inlineStr">
-        <is>
-          <t>서부T&amp;D</t>
-        </is>
-      </c>
-      <c r="H42" s="15" t="n">
-        <v>-36</v>
-      </c>
-      <c r="I42" s="15" t="n">
-        <v>-31540320</v>
-      </c>
-      <c r="J42" s="16" t="inlineStr">
-        <is>
-          <t>0.20%→0.10%</t>
-        </is>
-      </c>
-      <c r="K42" s="13" t="inlineStr">
-        <is>
-          <t>73→37</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="10" t="inlineStr">
-        <is>
-          <t>브이엠</t>
-        </is>
-      </c>
-      <c r="B43" s="11" t="n">
-        <v>13</v>
-      </c>
-      <c r="C43" s="11" t="n">
-        <v>92820000</v>
-      </c>
-      <c r="D43" s="12" t="inlineStr">
-        <is>
-          <t>3.37%→3.64%</t>
-        </is>
-      </c>
-      <c r="E43" s="13" t="inlineStr">
-        <is>
-          <t>150→163</t>
-        </is>
-      </c>
-      <c r="G43" s="14" t="inlineStr">
-        <is>
-          <t>채비  (편출)</t>
-        </is>
-      </c>
-      <c r="H43" s="15" t="n">
-        <v>-34</v>
-      </c>
-      <c r="I43" s="15" t="n">
-        <v>-15907920</v>
-      </c>
-      <c r="J43" s="16" t="inlineStr">
-        <is>
-          <t>0.05%→0.00%</t>
-        </is>
-      </c>
-      <c r="K43" s="13" t="inlineStr">
-        <is>
-          <t>34→0</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="10" t="inlineStr">
-        <is>
-          <t>테스</t>
-        </is>
-      </c>
-      <c r="B44" s="11" t="n">
-        <v>13</v>
-      </c>
-      <c r="C44" s="11" t="n">
-        <v>148184400</v>
-      </c>
-      <c r="D44" s="12" t="inlineStr">
-        <is>
-          <t>2.69%→3.14%</t>
-        </is>
-      </c>
-      <c r="E44" s="13" t="inlineStr">
-        <is>
-          <t>75→88</t>
-        </is>
-      </c>
-      <c r="G44" s="14" t="inlineStr">
-        <is>
-          <t>더핑크퐁컴퍼니</t>
-        </is>
-      </c>
-      <c r="H44" s="15" t="n">
-        <v>-34</v>
-      </c>
-      <c r="I44" s="15" t="n">
-        <v>-29816640</v>
-      </c>
-      <c r="J44" s="16" t="inlineStr">
-        <is>
-          <t>0.23%→0.13%</t>
-        </is>
-      </c>
-      <c r="K44" s="13" t="inlineStr">
-        <is>
-          <t>82→48</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="10" t="inlineStr">
-        <is>
-          <t>원익IPS</t>
-        </is>
-      </c>
-      <c r="B45" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="C45" s="11" t="n">
-        <v>103521600</v>
-      </c>
-      <c r="D45" s="12" t="inlineStr">
-        <is>
-          <t>2.31%→2.62%</t>
-        </is>
-      </c>
-      <c r="E45" s="13" t="inlineStr">
-        <is>
-          <t>85→97</t>
-        </is>
-      </c>
-      <c r="G45" s="14" t="inlineStr">
-        <is>
-          <t>다우데이타</t>
-        </is>
-      </c>
-      <c r="H45" s="15" t="n">
-        <v>-31</v>
-      </c>
-      <c r="I45" s="15" t="n">
-        <v>-46325160</v>
-      </c>
-      <c r="J45" s="16" t="inlineStr">
-        <is>
-          <t>0.35%→0.21%</t>
-        </is>
-      </c>
-      <c r="K45" s="13" t="inlineStr">
-        <is>
-          <t>75→44</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="10" t="inlineStr">
-        <is>
-          <t>코미코</t>
-        </is>
-      </c>
-      <c r="B46" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="C46" s="11" t="n">
-        <v>55776000</v>
-      </c>
-      <c r="D46" s="12" t="inlineStr">
-        <is>
-          <t>2.49%→2.65%</t>
-        </is>
-      </c>
-      <c r="E46" s="13" t="inlineStr">
-        <is>
-          <t>142→152</t>
-        </is>
-      </c>
-      <c r="G46" s="14" t="inlineStr">
-        <is>
-          <t>삼현  (편출)</t>
-        </is>
-      </c>
-      <c r="H46" s="15" t="n">
-        <v>-27</v>
-      </c>
-      <c r="I46" s="15" t="n">
-        <v>-68493600</v>
-      </c>
-      <c r="J46" s="16" t="inlineStr">
-        <is>
-          <t>0.22%→0.00%</t>
-        </is>
-      </c>
-      <c r="K46" s="13" t="inlineStr">
-        <is>
-          <t>27→0</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="10" t="inlineStr">
-        <is>
-          <t>HPSP</t>
-        </is>
-      </c>
-      <c r="B47" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="C47" s="11" t="n">
-        <v>32130000</v>
-      </c>
-      <c r="D47" s="12" t="inlineStr">
-        <is>
-          <t>1.15%→1.25%</t>
-        </is>
-      </c>
-      <c r="E47" s="13" t="inlineStr">
-        <is>
-          <t>114→124</t>
-        </is>
-      </c>
-      <c r="G47" s="14" t="inlineStr">
-        <is>
-          <t>실리콘투</t>
-        </is>
-      </c>
-      <c r="H47" s="15" t="n">
-        <v>-16</v>
-      </c>
-      <c r="I47" s="15" t="n">
-        <v>-48384000</v>
-      </c>
-      <c r="J47" s="16" t="inlineStr">
-        <is>
-          <t>0.81%→0.65%</t>
-        </is>
-      </c>
-      <c r="K47" s="13" t="inlineStr">
-        <is>
-          <t>85→69</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="10" t="inlineStr">
-        <is>
-          <t>피에스케이</t>
-        </is>
-      </c>
-      <c r="B48" s="11" t="n">
-        <v>9</v>
-      </c>
-      <c r="C48" s="11" t="n">
-        <v>114458400</v>
-      </c>
-      <c r="D48" s="12" t="inlineStr">
-        <is>
-          <t>2.52%→2.87%</t>
-        </is>
-      </c>
-      <c r="E48" s="13" t="inlineStr">
-        <is>
-          <t>63→72</t>
-        </is>
-      </c>
-      <c r="G48" s="14" t="inlineStr">
-        <is>
-          <t>하이록코리아</t>
-        </is>
-      </c>
-      <c r="H48" s="15" t="n">
-        <v>-14</v>
-      </c>
-      <c r="I48" s="15" t="n">
-        <v>-35103600</v>
-      </c>
-      <c r="J48" s="16" t="inlineStr">
-        <is>
-          <t>0.21%→0.10%</t>
-        </is>
-      </c>
-      <c r="K48" s="13" t="inlineStr">
-        <is>
-          <t>27→13</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="10" t="inlineStr">
-        <is>
-          <t>대주전자재료</t>
-        </is>
-      </c>
-      <c r="B49" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="C49" s="11" t="n">
-        <v>37396800</v>
-      </c>
-      <c r="D49" s="12" t="inlineStr">
-        <is>
-          <t>1.43%→1.54%</t>
-        </is>
-      </c>
-      <c r="E49" s="13" t="inlineStr">
-        <is>
-          <t>73→79</t>
-        </is>
-      </c>
-      <c r="G49" s="14" t="inlineStr">
-        <is>
-          <t>솔브레인홀딩스</t>
-        </is>
-      </c>
-      <c r="H49" s="15" t="n">
-        <v>-14</v>
-      </c>
-      <c r="I49" s="15" t="n">
-        <v>-38572800</v>
-      </c>
-      <c r="J49" s="16" t="inlineStr">
-        <is>
-          <t>0.72%→0.59%</t>
-        </is>
-      </c>
-      <c r="K49" s="13" t="inlineStr">
-        <is>
-          <t>83→69</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="10" t="inlineStr">
-        <is>
-          <t>씨엠티엑스</t>
-        </is>
-      </c>
-      <c r="B50" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="C50" s="11" t="n">
-        <v>34725600</v>
-      </c>
-      <c r="D50" s="12" t="inlineStr">
-        <is>
-          <t>0.84%→0.94%</t>
-        </is>
-      </c>
-      <c r="E50" s="13" t="inlineStr">
-        <is>
-          <t>46→52</t>
-        </is>
-      </c>
-      <c r="G50" s="14" t="inlineStr">
-        <is>
-          <t>디앤디파마텍</t>
-        </is>
-      </c>
-      <c r="H50" s="15" t="n">
-        <v>-10</v>
-      </c>
-      <c r="I50" s="15" t="n">
-        <v>-69048000</v>
-      </c>
-      <c r="J50" s="16" t="inlineStr">
-        <is>
-          <t>1.04%→0.82%</t>
-        </is>
-      </c>
-      <c r="K50" s="13" t="inlineStr">
-        <is>
-          <t>48→38</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="10" t="inlineStr">
-        <is>
-          <t>서진시스템</t>
-        </is>
-      </c>
-      <c r="B51" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="C51" s="11" t="n">
-        <v>18312000</v>
-      </c>
-      <c r="D51" s="12" t="inlineStr">
-        <is>
-          <t>7.25%→7.27%</t>
-        </is>
-      </c>
-      <c r="E51" s="13" t="inlineStr">
-        <is>
-          <t>629→634</t>
-        </is>
-      </c>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>피에스케이홀딩스</t>
-        </is>
-      </c>
-      <c r="H51" s="15" t="n">
-        <v>-7</v>
-      </c>
-      <c r="I51" s="15" t="n">
-        <v>-68325600</v>
-      </c>
-      <c r="J51" s="16" t="inlineStr">
-        <is>
-          <t>3.29%→3.05%</t>
-        </is>
-      </c>
-      <c r="K51" s="13" t="inlineStr">
-        <is>
-          <t>107→100</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="10" t="inlineStr">
-        <is>
-          <t>코스메카코리아  (신규)</t>
-        </is>
-      </c>
-      <c r="B52" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="C52" s="11" t="n">
-        <v>33768000</v>
-      </c>
-      <c r="D52" s="12" t="inlineStr">
-        <is>
-          <t>0.00%→0.11%</t>
-        </is>
-      </c>
-      <c r="E52" s="13" t="inlineStr">
-        <is>
-          <t>0→5</t>
-        </is>
-      </c>
-      <c r="G52" s="14" t="inlineStr">
-        <is>
-          <t>파크시스템스</t>
-        </is>
-      </c>
-      <c r="H52" s="15" t="n">
-        <v>-3</v>
-      </c>
-      <c r="I52" s="15" t="n">
-        <v>-68166000</v>
-      </c>
-      <c r="J52" s="16" t="inlineStr">
-        <is>
-          <t>1.93%→1.71%</t>
-        </is>
-      </c>
-      <c r="K52" s="13" t="inlineStr">
-        <is>
-          <t>27→24</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="19" customHeight="1">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 571억      주말 2026-07-10  vs  주초 2026-07-06      매수 0종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="n"/>
-      <c r="C54" s="4" t="n"/>
-      <c r="D54" s="4" t="n"/>
-      <c r="E54" s="4" t="n"/>
-      <c r="F54" s="4" t="n"/>
-      <c r="G54" s="4" t="n"/>
-      <c r="H54" s="4" t="n"/>
-      <c r="I54" s="4" t="n"/>
-      <c r="J54" s="4" t="n"/>
-      <c r="K54" s="4" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="17" t="inlineStr">
+      <c r="A39" s="17" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="19" customHeight="1">
-      <c r="A57" s="19" t="inlineStr">
+    <row r="41" ht="19" customHeight="1">
+      <c r="A41" s="19" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B57" s="20" t="n"/>
-      <c r="C57" s="20" t="n"/>
-      <c r="D57" s="20" t="n"/>
-      <c r="E57" s="20" t="n"/>
-      <c r="F57" s="20" t="n"/>
-      <c r="G57" s="20" t="n"/>
-      <c r="H57" s="20" t="n"/>
-      <c r="I57" s="20" t="n"/>
-      <c r="J57" s="20" t="n"/>
-      <c r="K57" s="20" t="n"/>
+      <c r="B41" s="20" t="n"/>
+      <c r="C41" s="20" t="n"/>
+      <c r="D41" s="20" t="n"/>
+      <c r="E41" s="20" t="n"/>
+      <c r="F41" s="20" t="n"/>
+      <c r="G41" s="20" t="n"/>
+      <c r="H41" s="20" t="n"/>
+      <c r="I41" s="20" t="n"/>
+      <c r="J41" s="20" t="n"/>
+      <c r="K41" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="16">
     <mergeCell ref="A22:K22"/>
     <mergeCell ref="A34:K34"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A21:K21"/>
-    <mergeCell ref="A54:K54"/>
-    <mergeCell ref="A55:K55"/>
+    <mergeCell ref="A39:K39"/>
     <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A57:K57"/>
     <mergeCell ref="A24:K24"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="G25:K25"/>
     <mergeCell ref="A33:K33"/>
-    <mergeCell ref="A37:E37"/>
-    <mergeCell ref="G37:K37"/>
+    <mergeCell ref="A38:K38"/>
+    <mergeCell ref="A41:K41"/>
     <mergeCell ref="A36:K36"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="G4:K4"/>

--- a/reports/pdf_weekly_20260710.xlsx
+++ b/reports/pdf_weekly_20260710.xlsx
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>주간 변화  ·  2026-07-06 ~ 2026-07-10  (5거래일)  ·  캡처 5/7  ·  대기: PLUS, TIGER</t>
+          <t>주간 변화  ·  2026-07-06 ~ 2026-07-10  (5거래일)  ·  캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
@@ -1618,78 +1618,768 @@
       </c>
     </row>
     <row r="36" ht="19" customHeight="1">
-      <c r="A36" s="19" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B36" s="20" t="n"/>
-      <c r="C36" s="20" t="n"/>
-      <c r="D36" s="20" t="n"/>
-      <c r="E36" s="20" t="n"/>
-      <c r="F36" s="20" t="n"/>
-      <c r="G36" s="20" t="n"/>
-      <c r="H36" s="20" t="n"/>
-      <c r="I36" s="20" t="n"/>
-      <c r="J36" s="20" t="n"/>
-      <c r="K36" s="20" t="n"/>
-    </row>
-    <row r="38" ht="19" customHeight="1">
-      <c r="A38" s="3" t="inlineStr">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 329억      주말 2026-07-10  vs  주초 2026-07-06      매수 14종목  /  매도 14종목</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="n"/>
+      <c r="C36" s="4" t="n"/>
+      <c r="D36" s="4" t="n"/>
+      <c r="E36" s="4" t="n"/>
+      <c r="F36" s="4" t="n"/>
+      <c r="G36" s="4" t="n"/>
+      <c r="H36" s="4" t="n"/>
+      <c r="I36" s="4" t="n"/>
+      <c r="J36" s="4" t="n"/>
+      <c r="K36" s="4" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+      <c r="E37" s="6" t="n"/>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H37" s="8" t="n"/>
+      <c r="I37" s="8" t="n"/>
+      <c r="J37" s="8" t="n"/>
+      <c r="K37" s="8" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G38" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H38" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I38" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J38" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K38" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>더블유씨피</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="n">
+        <v>121</v>
+      </c>
+      <c r="C39" s="11" t="n">
+        <v>87833900</v>
+      </c>
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>6.72%→6.95%</t>
+        </is>
+      </c>
+      <c r="E39" s="13" t="inlineStr">
+        <is>
+          <t>3,020→3,141</t>
+        </is>
+      </c>
+      <c r="G39" s="14" t="inlineStr">
+        <is>
+          <t>씨에스베어링</t>
+        </is>
+      </c>
+      <c r="H39" s="15" t="n">
+        <v>-318</v>
+      </c>
+      <c r="I39" s="15" t="n">
+        <v>-100551600</v>
+      </c>
+      <c r="J39" s="16" t="inlineStr">
+        <is>
+          <t>2.96%→2.64%</t>
+        </is>
+      </c>
+      <c r="K39" s="13" t="inlineStr">
+        <is>
+          <t>3,054→2,736</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>에이프로</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="n">
+        <v>91</v>
+      </c>
+      <c r="C40" s="11" t="n">
+        <v>21541975</v>
+      </c>
+      <c r="D40" s="12" t="inlineStr">
+        <is>
+          <t>0.37%→0.43%</t>
+        </is>
+      </c>
+      <c r="E40" s="13" t="inlineStr">
+        <is>
+          <t>510→601</t>
+        </is>
+      </c>
+      <c r="G40" s="14" t="inlineStr">
+        <is>
+          <t>LS증권</t>
+        </is>
+      </c>
+      <c r="H40" s="15" t="n">
+        <v>-101</v>
+      </c>
+      <c r="I40" s="15" t="n">
+        <v>-55544950</v>
+      </c>
+      <c r="J40" s="16" t="inlineStr">
+        <is>
+          <t>0.48%→0.31%</t>
+        </is>
+      </c>
+      <c r="K40" s="13" t="inlineStr">
+        <is>
+          <t>285→184</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>인텍플러스</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="n">
+        <v>54</v>
+      </c>
+      <c r="C41" s="11" t="n">
+        <v>177174000</v>
+      </c>
+      <c r="D41" s="12" t="inlineStr">
+        <is>
+          <t>1.87%→2.40%</t>
+        </is>
+      </c>
+      <c r="E41" s="13" t="inlineStr">
+        <is>
+          <t>186→240</t>
+        </is>
+      </c>
+      <c r="G41" s="14" t="inlineStr">
+        <is>
+          <t>씨어스</t>
+        </is>
+      </c>
+      <c r="H41" s="15" t="n">
+        <v>-36</v>
+      </c>
+      <c r="I41" s="15" t="n">
+        <v>-99450000</v>
+      </c>
+      <c r="J41" s="16" t="inlineStr">
+        <is>
+          <t>6.21%→5.87%</t>
+        </is>
+      </c>
+      <c r="K41" s="13" t="inlineStr">
+        <is>
+          <t>733→697</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>네패스아크</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="C42" s="11" t="n">
+        <v>47396000</v>
+      </c>
+      <c r="D42" s="12" t="inlineStr">
+        <is>
+          <t>0.19%→0.33%</t>
+        </is>
+      </c>
+      <c r="E42" s="13" t="inlineStr">
+        <is>
+          <t>21→37</t>
+        </is>
+      </c>
+      <c r="G42" s="14" t="inlineStr">
+        <is>
+          <t>서부T&amp;D</t>
+        </is>
+      </c>
+      <c r="H42" s="15" t="n">
+        <v>-36</v>
+      </c>
+      <c r="I42" s="15" t="n">
+        <v>-31518000</v>
+      </c>
+      <c r="J42" s="16" t="inlineStr">
+        <is>
+          <t>0.20%→0.10%</t>
+        </is>
+      </c>
+      <c r="K42" s="13" t="inlineStr">
+        <is>
+          <t>73→37</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>테스</t>
+        </is>
+      </c>
+      <c r="B43" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="C43" s="11" t="n">
+        <v>160225000</v>
+      </c>
+      <c r="D43" s="12" t="inlineStr">
+        <is>
+          <t>2.83%→3.30%</t>
+        </is>
+      </c>
+      <c r="E43" s="13" t="inlineStr">
+        <is>
+          <t>75→88</t>
+        </is>
+      </c>
+      <c r="G43" s="14" t="inlineStr">
+        <is>
+          <t>채비  (편출)</t>
+        </is>
+      </c>
+      <c r="H43" s="15" t="n">
+        <v>-34</v>
+      </c>
+      <c r="I43" s="15" t="n">
+        <v>-16010600</v>
+      </c>
+      <c r="J43" s="16" t="inlineStr">
+        <is>
+          <t>0.05%→0.00%</t>
+        </is>
+      </c>
+      <c r="K43" s="13" t="inlineStr">
+        <is>
+          <t>34→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>브이엠</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="C44" s="11" t="n">
+        <v>95693000</v>
+      </c>
+      <c r="D44" s="12" t="inlineStr">
+        <is>
+          <t>3.38%→3.66%</t>
+        </is>
+      </c>
+      <c r="E44" s="13" t="inlineStr">
+        <is>
+          <t>150→163</t>
+        </is>
+      </c>
+      <c r="G44" s="14" t="inlineStr">
+        <is>
+          <t>더핑크퐁컴퍼니</t>
+        </is>
+      </c>
+      <c r="H44" s="15" t="n">
+        <v>-34</v>
+      </c>
+      <c r="I44" s="15" t="n">
+        <v>-31501000</v>
+      </c>
+      <c r="J44" s="16" t="inlineStr">
+        <is>
+          <t>0.23%→0.14%</t>
+        </is>
+      </c>
+      <c r="K44" s="13" t="inlineStr">
+        <is>
+          <t>82→48</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>원익IPS</t>
+        </is>
+      </c>
+      <c r="B45" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="C45" s="11" t="n">
+        <v>106998000</v>
+      </c>
+      <c r="D45" s="12" t="inlineStr">
+        <is>
+          <t>2.32%→2.63%</t>
+        </is>
+      </c>
+      <c r="E45" s="13" t="inlineStr">
+        <is>
+          <t>85→97</t>
+        </is>
+      </c>
+      <c r="G45" s="14" t="inlineStr">
+        <is>
+          <t>다우데이타</t>
+        </is>
+      </c>
+      <c r="H45" s="15" t="n">
+        <v>-31</v>
+      </c>
+      <c r="I45" s="15" t="n">
+        <v>-46165200</v>
+      </c>
+      <c r="J45" s="16" t="inlineStr">
+        <is>
+          <t>0.34%→0.20%</t>
+        </is>
+      </c>
+      <c r="K45" s="13" t="inlineStr">
+        <is>
+          <t>75→44</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>HPSP</t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C46" s="11" t="n">
+        <v>33405000</v>
+      </c>
+      <c r="D46" s="12" t="inlineStr">
+        <is>
+          <t>1.17%→1.26%</t>
+        </is>
+      </c>
+      <c r="E46" s="13" t="inlineStr">
+        <is>
+          <t>114→124</t>
+        </is>
+      </c>
+      <c r="G46" s="14" t="inlineStr">
+        <is>
+          <t>삼현  (편출)</t>
+        </is>
+      </c>
+      <c r="H46" s="15" t="n">
+        <v>-27</v>
+      </c>
+      <c r="I46" s="15" t="n">
+        <v>-77571000</v>
+      </c>
+      <c r="J46" s="16" t="inlineStr">
+        <is>
+          <t>0.24%→0.00%</t>
+        </is>
+      </c>
+      <c r="K46" s="13" t="inlineStr">
+        <is>
+          <t>27→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>코미코</t>
+        </is>
+      </c>
+      <c r="B47" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C47" s="11" t="n">
+        <v>64515000</v>
+      </c>
+      <c r="D47" s="12" t="inlineStr">
+        <is>
+          <t>2.81%→2.99%</t>
+        </is>
+      </c>
+      <c r="E47" s="13" t="inlineStr">
+        <is>
+          <t>142→152</t>
+        </is>
+      </c>
+      <c r="G47" s="14" t="inlineStr">
+        <is>
+          <t>실리콘투</t>
+        </is>
+      </c>
+      <c r="H47" s="15" t="n">
+        <v>-16</v>
+      </c>
+      <c r="I47" s="15" t="n">
+        <v>-48348000</v>
+      </c>
+      <c r="J47" s="16" t="inlineStr">
+        <is>
+          <t>0.79%→0.64%</t>
+        </is>
+      </c>
+      <c r="K47" s="13" t="inlineStr">
+        <is>
+          <t>85→69</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>피에스케이</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C48" s="11" t="n">
+        <v>116433000</v>
+      </c>
+      <c r="D48" s="12" t="inlineStr">
+        <is>
+          <t>2.50%→2.84%</t>
+        </is>
+      </c>
+      <c r="E48" s="13" t="inlineStr">
+        <is>
+          <t>63→72</t>
+        </is>
+      </c>
+      <c r="G48" s="14" t="inlineStr">
+        <is>
+          <t>솔브레인홀딩스</t>
+        </is>
+      </c>
+      <c r="H48" s="15" t="n">
+        <v>-14</v>
+      </c>
+      <c r="I48" s="15" t="n">
+        <v>-40162500</v>
+      </c>
+      <c r="J48" s="16" t="inlineStr">
+        <is>
+          <t>0.73%→0.60%</t>
+        </is>
+      </c>
+      <c r="K48" s="13" t="inlineStr">
+        <is>
+          <t>83→69</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>대주전자재료</t>
+        </is>
+      </c>
+      <c r="B49" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C49" s="11" t="n">
+        <v>38046000</v>
+      </c>
+      <c r="D49" s="12" t="inlineStr">
+        <is>
+          <t>1.42%→1.53%</t>
+        </is>
+      </c>
+      <c r="E49" s="13" t="inlineStr">
+        <is>
+          <t>73→79</t>
+        </is>
+      </c>
+      <c r="G49" s="14" t="inlineStr">
+        <is>
+          <t>하이록코리아</t>
+        </is>
+      </c>
+      <c r="H49" s="15" t="n">
+        <v>-14</v>
+      </c>
+      <c r="I49" s="15" t="n">
+        <v>-35759500</v>
+      </c>
+      <c r="J49" s="16" t="inlineStr">
+        <is>
+          <t>0.21%→0.10%</t>
+        </is>
+      </c>
+      <c r="K49" s="13" t="inlineStr">
+        <is>
+          <t>27→13</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>씨엠티엑스</t>
+        </is>
+      </c>
+      <c r="B50" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C50" s="11" t="n">
+        <v>38709000</v>
+      </c>
+      <c r="D50" s="12" t="inlineStr">
+        <is>
+          <t>0.91%→1.02%</t>
+        </is>
+      </c>
+      <c r="E50" s="13" t="inlineStr">
+        <is>
+          <t>46→52</t>
+        </is>
+      </c>
+      <c r="G50" s="14" t="inlineStr">
+        <is>
+          <t>디앤디파마텍</t>
+        </is>
+      </c>
+      <c r="H50" s="15" t="n">
+        <v>-10</v>
+      </c>
+      <c r="I50" s="15" t="n">
+        <v>-73610000</v>
+      </c>
+      <c r="J50" s="16" t="inlineStr">
+        <is>
+          <t>1.08%→0.85%</t>
+        </is>
+      </c>
+      <c r="K50" s="13" t="inlineStr">
+        <is>
+          <t>48→38</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>서진시스템</t>
+        </is>
+      </c>
+      <c r="B51" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C51" s="11" t="n">
+        <v>17722500</v>
+      </c>
+      <c r="D51" s="12" t="inlineStr">
+        <is>
+          <t>6.83%→6.85%</t>
+        </is>
+      </c>
+      <c r="E51" s="13" t="inlineStr">
+        <is>
+          <t>629→634</t>
+        </is>
+      </c>
+      <c r="G51" s="14" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="H51" s="15" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I51" s="15" t="n">
+        <v>-68544000</v>
+      </c>
+      <c r="J51" s="16" t="inlineStr">
+        <is>
+          <t>3.21%→2.98%</t>
+        </is>
+      </c>
+      <c r="K51" s="13" t="inlineStr">
+        <is>
+          <t>107→100</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="10" t="inlineStr">
+        <is>
+          <t>코스메카코리아  (신규)</t>
+        </is>
+      </c>
+      <c r="B52" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C52" s="11" t="n">
+        <v>36337500</v>
+      </c>
+      <c r="D52" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.11%</t>
+        </is>
+      </c>
+      <c r="E52" s="13" t="inlineStr">
+        <is>
+          <t>0→5</t>
+        </is>
+      </c>
+      <c r="G52" s="14" t="inlineStr">
+        <is>
+          <t>파크시스템스</t>
+        </is>
+      </c>
+      <c r="H52" s="15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I52" s="15" t="n">
+        <v>-73567500</v>
+      </c>
+      <c r="J52" s="16" t="inlineStr">
+        <is>
+          <t>2.03%→1.79%</t>
+        </is>
+      </c>
+      <c r="K52" s="13" t="inlineStr">
+        <is>
+          <t>27→24</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="19" customHeight="1">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 568억      주말 2026-07-10  vs  주초 2026-07-06      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
-      <c r="B38" s="4" t="n"/>
-      <c r="C38" s="4" t="n"/>
-      <c r="D38" s="4" t="n"/>
-      <c r="E38" s="4" t="n"/>
-      <c r="F38" s="4" t="n"/>
-      <c r="G38" s="4" t="n"/>
-      <c r="H38" s="4" t="n"/>
-      <c r="I38" s="4" t="n"/>
-      <c r="J38" s="4" t="n"/>
-      <c r="K38" s="4" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="17" t="inlineStr">
+      <c r="B54" s="4" t="n"/>
+      <c r="C54" s="4" t="n"/>
+      <c r="D54" s="4" t="n"/>
+      <c r="E54" s="4" t="n"/>
+      <c r="F54" s="4" t="n"/>
+      <c r="G54" s="4" t="n"/>
+      <c r="H54" s="4" t="n"/>
+      <c r="I54" s="4" t="n"/>
+      <c r="J54" s="4" t="n"/>
+      <c r="K54" s="4" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="17" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="19" customHeight="1">
-      <c r="A41" s="19" t="inlineStr">
+    <row r="57" ht="19" customHeight="1">
+      <c r="A57" s="19" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B41" s="20" t="n"/>
-      <c r="C41" s="20" t="n"/>
-      <c r="D41" s="20" t="n"/>
-      <c r="E41" s="20" t="n"/>
-      <c r="F41" s="20" t="n"/>
-      <c r="G41" s="20" t="n"/>
-      <c r="H41" s="20" t="n"/>
-      <c r="I41" s="20" t="n"/>
-      <c r="J41" s="20" t="n"/>
-      <c r="K41" s="20" t="n"/>
+      <c r="B57" s="20" t="n"/>
+      <c r="C57" s="20" t="n"/>
+      <c r="D57" s="20" t="n"/>
+      <c r="E57" s="20" t="n"/>
+      <c r="F57" s="20" t="n"/>
+      <c r="G57" s="20" t="n"/>
+      <c r="H57" s="20" t="n"/>
+      <c r="I57" s="20" t="n"/>
+      <c r="J57" s="20" t="n"/>
+      <c r="K57" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="18">
     <mergeCell ref="A22:K22"/>
     <mergeCell ref="A34:K34"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A21:K21"/>
-    <mergeCell ref="A39:K39"/>
+    <mergeCell ref="A54:K54"/>
+    <mergeCell ref="A55:K55"/>
     <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A57:K57"/>
     <mergeCell ref="A24:K24"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="G25:K25"/>
     <mergeCell ref="A33:K33"/>
-    <mergeCell ref="A38:K38"/>
-    <mergeCell ref="A41:K41"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="G37:K37"/>
     <mergeCell ref="A36:K36"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="G4:K4"/>

--- a/reports/pdf_weekly_20260710.xlsx
+++ b/reports/pdf_weekly_20260710.xlsx
@@ -1818,23 +1818,23 @@
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
-          <t>씨어스</t>
+          <t>서부T&amp;D</t>
         </is>
       </c>
       <c r="H41" s="15" t="n">
         <v>-36</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-99450000</v>
+        <v>-31518000</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
-          <t>6.21%→5.87%</t>
+          <t>0.20%→0.10%</t>
         </is>
       </c>
       <c r="K41" s="13" t="inlineStr">
         <is>
-          <t>733→697</t>
+          <t>73→37</t>
         </is>
       </c>
     </row>
@@ -1862,23 +1862,23 @@
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
-          <t>서부T&amp;D</t>
+          <t>씨어스</t>
         </is>
       </c>
       <c r="H42" s="15" t="n">
         <v>-36</v>
       </c>
       <c r="I42" s="15" t="n">
-        <v>-31518000</v>
+        <v>-99450000</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
-          <t>0.20%→0.10%</t>
+          <t>6.21%→5.87%</t>
         </is>
       </c>
       <c r="K42" s="13" t="inlineStr">
         <is>
-          <t>73→37</t>
+          <t>733→697</t>
         </is>
       </c>
     </row>
@@ -1906,23 +1906,23 @@
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
-          <t>채비  (편출)</t>
+          <t>더핑크퐁컴퍼니</t>
         </is>
       </c>
       <c r="H43" s="15" t="n">
         <v>-34</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>-16010600</v>
+        <v>-31501000</v>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
-          <t>0.05%→0.00%</t>
+          <t>0.23%→0.14%</t>
         </is>
       </c>
       <c r="K43" s="13" t="inlineStr">
         <is>
-          <t>34→0</t>
+          <t>82→48</t>
         </is>
       </c>
     </row>
@@ -1950,23 +1950,23 @@
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
-          <t>더핑크퐁컴퍼니</t>
+          <t>채비  (편출)</t>
         </is>
       </c>
       <c r="H44" s="15" t="n">
         <v>-34</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-31501000</v>
+        <v>-16010600</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
-          <t>0.23%→0.14%</t>
+          <t>0.05%→0.00%</t>
         </is>
       </c>
       <c r="K44" s="13" t="inlineStr">
         <is>
-          <t>82→48</t>
+          <t>34→0</t>
         </is>
       </c>
     </row>
@@ -2126,23 +2126,23 @@
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
-          <t>솔브레인홀딩스</t>
+          <t>하이록코리아</t>
         </is>
       </c>
       <c r="H48" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-40162500</v>
+        <v>-35759500</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
-          <t>0.73%→0.60%</t>
+          <t>0.21%→0.10%</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
         <is>
-          <t>83→69</t>
+          <t>27→13</t>
         </is>
       </c>
     </row>
@@ -2170,23 +2170,23 @@
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>하이록코리아</t>
+          <t>솔브레인홀딩스</t>
         </is>
       </c>
       <c r="H49" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-35759500</v>
+        <v>-40162500</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>0.21%→0.10%</t>
+          <t>0.73%→0.60%</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
-          <t>27→13</t>
+          <t>83→69</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_weekly_20260710.xlsx
+++ b/reports/pdf_weekly_20260710.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,448억      주말 2026-07-10  vs  주초 2026-07-06      매수 14종목  /  매도 14종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      주말 2026-07-10  vs  주초 2026-07-06      매수 14종목  /  매도 14종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -669,8 +669,10 @@
       <c r="B6" s="11" t="n">
         <v>109</v>
       </c>
-      <c r="C6" s="11" t="n">
-        <v>877815150</v>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -690,8 +692,10 @@
       <c r="H6" s="15" t="n">
         <v>-54</v>
       </c>
-      <c r="I6" s="15" t="n">
-        <v>-818341920</v>
+      <c r="I6" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -713,8 +717,10 @@
       <c r="B7" s="11" t="n">
         <v>93</v>
       </c>
-      <c r="C7" s="11" t="n">
-        <v>970352700</v>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -734,8 +740,10 @@
       <c r="H7" s="15" t="n">
         <v>-52</v>
       </c>
-      <c r="I7" s="15" t="n">
-        <v>-1464392800</v>
+      <c r="I7" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -757,8 +765,10 @@
       <c r="B8" s="11" t="n">
         <v>66</v>
       </c>
-      <c r="C8" s="11" t="n">
-        <v>2283200700</v>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -778,8 +788,10 @@
       <c r="H8" s="15" t="n">
         <v>-37</v>
       </c>
-      <c r="I8" s="15" t="n">
-        <v>-1169407200</v>
+      <c r="I8" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -801,8 +813,10 @@
       <c r="B9" s="11" t="n">
         <v>60</v>
       </c>
-      <c r="C9" s="11" t="n">
-        <v>4364004000</v>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -822,8 +836,10 @@
       <c r="H9" s="15" t="n">
         <v>-25</v>
       </c>
-      <c r="I9" s="15" t="n">
-        <v>-3672125000</v>
+      <c r="I9" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -845,8 +861,10 @@
       <c r="B10" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="C10" s="11" t="n">
-        <v>1842241800</v>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -866,8 +884,10 @@
       <c r="H10" s="15" t="n">
         <v>-23</v>
       </c>
-      <c r="I10" s="15" t="n">
-        <v>-2444065100</v>
+      <c r="I10" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -889,8 +909,10 @@
       <c r="B11" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="C11" s="11" t="n">
-        <v>1126456000</v>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -910,8 +932,10 @@
       <c r="H11" s="15" t="n">
         <v>-22</v>
       </c>
-      <c r="I11" s="15" t="n">
-        <v>-460205900</v>
+      <c r="I11" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -933,8 +957,10 @@
       <c r="B12" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="C12" s="11" t="n">
-        <v>1259361600</v>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -954,8 +980,10 @@
       <c r="H12" s="15" t="n">
         <v>-20</v>
       </c>
-      <c r="I12" s="15" t="n">
-        <v>-844842000</v>
+      <c r="I12" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -971,23 +999,25 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>이엔에프테크놀로지</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="11" t="n">
-        <v>520378100</v>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>0.39%→0.60%</t>
+          <t>0.49%→0.62%</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>45→56</t>
+          <t>59→70</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -998,8 +1028,10 @@
       <c r="H13" s="15" t="n">
         <v>-19</v>
       </c>
-      <c r="I13" s="15" t="n">
-        <v>-1287624300</v>
+      <c r="I13" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1015,23 +1047,25 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>이엔에프테크놀로지</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="C14" s="11" t="n">
-        <v>430119800</v>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>0.49%→0.62%</t>
+          <t>0.39%→0.60%</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>59→70</t>
+          <t>45→56</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -1042,8 +1076,10 @@
       <c r="H14" s="15" t="n">
         <v>-17</v>
       </c>
-      <c r="I14" s="15" t="n">
-        <v>-843829000</v>
+      <c r="I14" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -1065,8 +1101,10 @@
       <c r="B15" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="C15" s="11" t="n">
-        <v>436603000</v>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -1086,8 +1124,10 @@
       <c r="H15" s="15" t="n">
         <v>-16</v>
       </c>
-      <c r="I15" s="15" t="n">
-        <v>-2466857600</v>
+      <c r="I15" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1109,8 +1149,10 @@
       <c r="B16" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="C16" s="11" t="n">
-        <v>415836500</v>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
@@ -1130,8 +1172,10 @@
       <c r="H16" s="15" t="n">
         <v>-12</v>
       </c>
-      <c r="I16" s="15" t="n">
-        <v>-427891200</v>
+      <c r="I16" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1153,8 +1197,10 @@
       <c r="B17" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="C17" s="11" t="n">
-        <v>955461600</v>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
@@ -1174,8 +1220,10 @@
       <c r="H17" s="15" t="n">
         <v>-10</v>
       </c>
-      <c r="I17" s="15" t="n">
-        <v>-432551000</v>
+      <c r="I17" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
@@ -1191,23 +1239,25 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="C18" s="11" t="n">
-        <v>1519500000</v>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>3.60%→3.93%</t>
+          <t>2.69%→3.13%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>52→57</t>
+          <t>39→44</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -1218,8 +1268,10 @@
       <c r="H18" s="15" t="n">
         <v>-6</v>
       </c>
-      <c r="I18" s="15" t="n">
-        <v>-920817000</v>
+      <c r="I18" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -1235,23 +1287,25 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="C19" s="11" t="n">
-        <v>1565085000</v>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>2.69%→3.13%</t>
+          <t>3.60%→3.93%</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>39→44</t>
+          <t>52→57</t>
         </is>
       </c>
       <c r="G19" s="14" t="inlineStr">
@@ -1262,8 +1316,10 @@
       <c r="H19" s="15" t="n">
         <v>-4</v>
       </c>
-      <c r="I19" s="15" t="n">
-        <v>-478946400</v>
+      <c r="I19" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -1279,7 +1335,7 @@
     <row r="21" ht="19" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,303억      주말 2026-07-10  vs  주초 2026-07-06      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      주말 2026-07-10  vs  주초 2026-07-06      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B21" s="4" t="n"/>
@@ -1303,7 +1359,7 @@
     <row r="24" ht="19" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,562억      주말 2026-07-10  vs  주초 2026-07-06      매수 4종목  /  매도 5종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      주말 2026-07-10  vs  주초 2026-07-06      매수 4종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B24" s="4" t="n"/>
@@ -1398,8 +1454,10 @@
       <c r="B27" s="11" t="n">
         <v>201</v>
       </c>
-      <c r="C27" s="11" t="n">
-        <v>5330158200</v>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
@@ -1419,8 +1477,10 @@
       <c r="H27" s="15" t="n">
         <v>-86</v>
       </c>
-      <c r="I27" s="15" t="n">
-        <v>-6197701800</v>
+      <c r="I27" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
@@ -1442,8 +1502,10 @@
       <c r="B28" s="11" t="n">
         <v>139</v>
       </c>
-      <c r="C28" s="11" t="n">
-        <v>6665411400</v>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
@@ -1463,8 +1525,10 @@
       <c r="H28" s="15" t="n">
         <v>-81</v>
       </c>
-      <c r="I28" s="15" t="n">
-        <v>-4323771900</v>
+      <c r="I28" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
@@ -1486,8 +1550,10 @@
       <c r="B29" s="11" t="n">
         <v>35</v>
       </c>
-      <c r="C29" s="11" t="n">
-        <v>7429905000</v>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
@@ -1507,8 +1573,10 @@
       <c r="H29" s="15" t="n">
         <v>-66</v>
       </c>
-      <c r="I29" s="15" t="n">
-        <v>-6574590000</v>
+      <c r="I29" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
@@ -1530,8 +1598,10 @@
       <c r="B30" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="C30" s="11" t="n">
-        <v>1380457800</v>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
@@ -1551,8 +1621,10 @@
       <c r="H30" s="15" t="n">
         <v>-58</v>
       </c>
-      <c r="I30" s="15" t="n">
-        <v>-1402579200</v>
+      <c r="I30" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
@@ -1579,8 +1651,10 @@
       <c r="H31" s="15" t="n">
         <v>-40</v>
       </c>
-      <c r="I31" s="15" t="n">
-        <v>-4163220000</v>
+      <c r="I31" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
@@ -1596,7 +1670,7 @@
     <row r="33" ht="19" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,548억      주말 2026-07-10  vs  주초 2026-07-06      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      주말 2026-07-10  vs  주초 2026-07-06      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B33" s="4" t="n"/>
@@ -1620,7 +1694,7 @@
     <row r="36" ht="19" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 329억      주말 2026-07-10  vs  주초 2026-07-06      매수 14종목  /  매도 14종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      주말 2026-07-10  vs  주초 2026-07-06      매수 14종목  /  매도 14종목</t>
         </is>
       </c>
       <c r="B36" s="4" t="n"/>
@@ -1715,12 +1789,14 @@
       <c r="B39" s="11" t="n">
         <v>121</v>
       </c>
-      <c r="C39" s="11" t="n">
-        <v>87833900</v>
+      <c r="C39" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>6.72%→6.95%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E39" s="13" t="inlineStr">
@@ -1736,12 +1812,14 @@
       <c r="H39" s="15" t="n">
         <v>-318</v>
       </c>
-      <c r="I39" s="15" t="n">
-        <v>-100551600</v>
+      <c r="I39" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
-          <t>2.96%→2.64%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K39" s="13" t="inlineStr">
@@ -1759,12 +1837,14 @@
       <c r="B40" s="11" t="n">
         <v>91</v>
       </c>
-      <c r="C40" s="11" t="n">
-        <v>21541975</v>
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>0.37%→0.43%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
@@ -1780,12 +1860,14 @@
       <c r="H40" s="15" t="n">
         <v>-101</v>
       </c>
-      <c r="I40" s="15" t="n">
-        <v>-55544950</v>
+      <c r="I40" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
-          <t>0.48%→0.31%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K40" s="13" t="inlineStr">
@@ -1803,12 +1885,14 @@
       <c r="B41" s="11" t="n">
         <v>54</v>
       </c>
-      <c r="C41" s="11" t="n">
-        <v>177174000</v>
+      <c r="C41" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>1.87%→2.40%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr">
@@ -1818,23 +1902,25 @@
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
-          <t>서부T&amp;D</t>
+          <t>씨어스</t>
         </is>
       </c>
       <c r="H41" s="15" t="n">
         <v>-36</v>
       </c>
-      <c r="I41" s="15" t="n">
-        <v>-31518000</v>
+      <c r="I41" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
-          <t>0.20%→0.10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K41" s="13" t="inlineStr">
         <is>
-          <t>73→37</t>
+          <t>733→697</t>
         </is>
       </c>
     </row>
@@ -1847,12 +1933,14 @@
       <c r="B42" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="C42" s="11" t="n">
-        <v>47396000</v>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>0.19%→0.33%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
@@ -1862,23 +1950,25 @@
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
-          <t>씨어스</t>
+          <t>서부T&amp;D</t>
         </is>
       </c>
       <c r="H42" s="15" t="n">
         <v>-36</v>
       </c>
-      <c r="I42" s="15" t="n">
-        <v>-99450000</v>
+      <c r="I42" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
-          <t>6.21%→5.87%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K42" s="13" t="inlineStr">
         <is>
-          <t>733→697</t>
+          <t>73→37</t>
         </is>
       </c>
     </row>
@@ -1891,12 +1981,14 @@
       <c r="B43" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="C43" s="11" t="n">
-        <v>160225000</v>
+      <c r="C43" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>2.83%→3.30%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
@@ -1912,12 +2004,14 @@
       <c r="H43" s="15" t="n">
         <v>-34</v>
       </c>
-      <c r="I43" s="15" t="n">
-        <v>-31501000</v>
+      <c r="I43" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
-          <t>0.23%→0.14%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K43" s="13" t="inlineStr">
@@ -1935,12 +2029,14 @@
       <c r="B44" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="C44" s="11" t="n">
-        <v>95693000</v>
+      <c r="C44" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>3.38%→3.66%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
@@ -1956,12 +2052,14 @@
       <c r="H44" s="15" t="n">
         <v>-34</v>
       </c>
-      <c r="I44" s="15" t="n">
-        <v>-16010600</v>
+      <c r="I44" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
-          <t>0.05%→0.00%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K44" s="13" t="inlineStr">
@@ -1979,12 +2077,14 @@
       <c r="B45" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="C45" s="11" t="n">
-        <v>106998000</v>
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>2.32%→2.63%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
@@ -2000,12 +2100,14 @@
       <c r="H45" s="15" t="n">
         <v>-31</v>
       </c>
-      <c r="I45" s="15" t="n">
-        <v>-46165200</v>
+      <c r="I45" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>0.34%→0.20%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K45" s="13" t="inlineStr">
@@ -2017,23 +2119,25 @@
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>HPSP</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="B46" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="C46" s="11" t="n">
-        <v>33405000</v>
+      <c r="C46" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>1.17%→1.26%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>114→124</t>
+          <t>142→152</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
@@ -2044,12 +2148,14 @@
       <c r="H46" s="15" t="n">
         <v>-27</v>
       </c>
-      <c r="I46" s="15" t="n">
-        <v>-77571000</v>
+      <c r="I46" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>0.24%→0.00%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
@@ -2061,23 +2167,25 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>HPSP</t>
         </is>
       </c>
       <c r="B47" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="C47" s="11" t="n">
-        <v>64515000</v>
+      <c r="C47" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>2.81%→2.99%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
         <is>
-          <t>142→152</t>
+          <t>114→124</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
@@ -2088,12 +2196,14 @@
       <c r="H47" s="15" t="n">
         <v>-16</v>
       </c>
-      <c r="I47" s="15" t="n">
-        <v>-48348000</v>
+      <c r="I47" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>0.79%→0.64%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
@@ -2111,12 +2221,14 @@
       <c r="B48" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="C48" s="11" t="n">
-        <v>116433000</v>
+      <c r="C48" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>2.50%→2.84%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
@@ -2132,12 +2244,14 @@
       <c r="H48" s="15" t="n">
         <v>-14</v>
       </c>
-      <c r="I48" s="15" t="n">
-        <v>-35759500</v>
+      <c r="I48" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
-          <t>0.21%→0.10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
@@ -2155,12 +2269,14 @@
       <c r="B49" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="C49" s="11" t="n">
-        <v>38046000</v>
+      <c r="C49" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>1.42%→1.53%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
@@ -2176,12 +2292,14 @@
       <c r="H49" s="15" t="n">
         <v>-14</v>
       </c>
-      <c r="I49" s="15" t="n">
-        <v>-40162500</v>
+      <c r="I49" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>0.73%→0.60%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
@@ -2199,12 +2317,14 @@
       <c r="B50" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="C50" s="11" t="n">
-        <v>38709000</v>
+      <c r="C50" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>0.91%→1.02%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
@@ -2220,12 +2340,14 @@
       <c r="H50" s="15" t="n">
         <v>-10</v>
       </c>
-      <c r="I50" s="15" t="n">
-        <v>-73610000</v>
+      <c r="I50" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>1.08%→0.85%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
@@ -2243,12 +2365,14 @@
       <c r="B51" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="C51" s="11" t="n">
-        <v>17722500</v>
+      <c r="C51" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>6.83%→6.85%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
@@ -2264,12 +2388,14 @@
       <c r="H51" s="15" t="n">
         <v>-7</v>
       </c>
-      <c r="I51" s="15" t="n">
-        <v>-68544000</v>
+      <c r="I51" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
-          <t>3.21%→2.98%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K51" s="13" t="inlineStr">
@@ -2287,12 +2413,14 @@
       <c r="B52" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="C52" s="11" t="n">
-        <v>36337500</v>
+      <c r="C52" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.11%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
@@ -2308,12 +2436,14 @@
       <c r="H52" s="15" t="n">
         <v>-3</v>
       </c>
-      <c r="I52" s="15" t="n">
-        <v>-73567500</v>
+      <c r="I52" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
-          <t>2.03%→1.79%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
@@ -2325,7 +2455,7 @@
     <row r="54" ht="19" customHeight="1">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 568억      주말 2026-07-10  vs  주초 2026-07-06      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      주말 2026-07-10  vs  주초 2026-07-06      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B54" s="4" t="n"/>
